--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487682_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487682_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9583</v>
+        <v>6.8394</v>
       </c>
       <c r="E2" t="n">
-        <v>7.474</v>
+        <v>6.5731</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4843</v>
+        <v>0.2663</v>
       </c>
       <c r="G2" t="n">
         <v>1.6199</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1646</v>
+        <v>0.0457</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5731000000000001</v>
+        <v>-0.3278</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5916</v>
+        <v>0.3735</v>
       </c>
       <c r="V2" t="n">
         <v>2.4573</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7398</v>
+        <v>6.3037</v>
       </c>
       <c r="E3" t="n">
-        <v>6.155</v>
+        <v>6.5554</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4152</v>
+        <v>-0.2517</v>
       </c>
       <c r="G3" t="n">
         <v>0.6239</v>
@@ -688,13 +688,13 @@
         <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8488</v>
+        <v>-0.2849</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5193</v>
+        <v>-0.1189</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3295</v>
+        <v>-0.166</v>
       </c>
       <c r="V3" t="n">
         <v>3.4423</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2261</v>
+        <v>0.882</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2069</v>
+        <v>1.2802</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9809</v>
+        <v>-0.3982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0934</v>
+        <v>-0.2758</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6896</v>
+        <v>-1.4014</v>
       </c>
       <c r="I4" t="n">
-        <v>0.783</v>
+        <v>1.1256</v>
       </c>
       <c r="J4" t="n">
-        <v>0.044</v>
+        <v>1.4667</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6055</v>
+        <v>-0.482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6495</v>
+        <v>1.9486</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0494</v>
+        <v>-1.7425</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.9195</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1335</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8804</v>
+        <v>-0.6362</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8809</v>
+        <v>-0.4686</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0004</v>
+        <v>-0.1677</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9418</v>
+        <v>0.0478</v>
       </c>
       <c r="W4" t="n">
         <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1005</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5805</v>
+        <v>1.1059</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.48</v>
+        <v>-1.0354</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2758</v>
+        <v>0.0934</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4014</v>
+        <v>-0.6896</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1256</v>
+        <v>0.783</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4667</v>
+        <v>0.044</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.482</v>
+        <v>-0.6055</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9486</v>
+        <v>0.6495</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7425</v>
+        <v>0.0494</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9195</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8231000000000001</v>
+        <v>0.1335</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4177</v>
+        <v>0.7248</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1683</v>
+        <v>0.7798</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2494</v>
+        <v>-0.055</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0478</v>
+        <v>-0.9418</v>
       </c>
       <c r="W5" t="n">
         <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2343</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7917</v>
+        <v>-0.3363</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9114</v>
+        <v>1.6121</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7031</v>
+        <v>-1.9484</v>
       </c>
       <c r="G6" t="n">
         <v>1.9406</v>
@@ -922,13 +922,13 @@
         <v>2.7164</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5404</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3807</v>
+        <v>-0.68</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8403</v>
+        <v>0.595</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0278</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.574</v>
+        <v>-2.3465</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1341</v>
+        <v>0.3343</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.708</v>
+        <v>-2.6808</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8292</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0911</v>
+        <v>0.3185</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2731</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8358</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.206</v>
+        <v>-2.6514</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8743</v>
+        <v>-1.6741</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3317</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0548</v>
@@ -1078,13 +1078,13 @@
         <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2667</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7257</v>
+        <v>-0.5255</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.541</v>
+        <v>-0.1867</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4964</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.7166</v>
+        <v>-5.4163</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2041</v>
+        <v>-3.9038</v>
       </c>
       <c r="F9" t="n">
         <v>-1.5125</v>
@@ -1156,10 +1156,10 @@
         <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4733</v>
+        <v>-0.173</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4116</v>
+        <v>-0.1113</v>
       </c>
       <c r="U9" t="n">
         <v>-0.0617</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1718</v>
+        <v>-6.7803</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3387</v>
+        <v>-3.8382</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.833</v>
+        <v>-2.9421</v>
       </c>
       <c r="G10" t="n">
         <v>-7.0793</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8006</v>
+        <v>-0.4091</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.701</v>
+        <v>-0.2005</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.2086</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6502</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4354</v>
+        <v>-3.4352</v>
       </c>
       <c r="E11" t="n">
-        <v>8.044800000000002</v>
+        <v>8.044899999999998</v>
       </c>
       <c r="F11" t="n">
         <v>-11.4801</v>
@@ -1318,7 +1318,7 @@
         <v>-1.3797</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1686</v>
+        <v>0.1682</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2285</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3088</v>
+        <v>5.588</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2034</v>
+        <v>4.4036</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1054</v>
+        <v>1.1844</v>
       </c>
       <c r="G12" t="n">
         <v>3.1757</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0242</v>
+        <v>0.3034</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2524</v>
+        <v>-0.0522</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2766</v>
+        <v>0.3556</v>
       </c>
       <c r="V12" t="n">
         <v>4.0492</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5257</v>
+        <v>2.7047</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3609</v>
+        <v>1.461</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1648</v>
+        <v>1.2437</v>
       </c>
       <c r="G13" t="n">
         <v>1.4888</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0004</v>
+        <v>0.1786</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0004</v>
+        <v>0.0785</v>
       </c>
       <c r="V13" t="n">
         <v>1.0373</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5641</v>
+        <v>1.1374</v>
       </c>
       <c r="E14" t="n">
-        <v>2.157</v>
+        <v>4.5693</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5929</v>
+        <v>-3.4319</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7019</v>
+        <v>0.7544</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1022</v>
+        <v>-0.1565</v>
       </c>
       <c r="I14" t="n">
-        <v>1.804</v>
+        <v>0.9109</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3277</v>
+        <v>1.9805</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0463</v>
+        <v>1.1864</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2813</v>
+        <v>0.7942</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6258</v>
+        <v>-1.2262</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1485</v>
+        <v>-1.3429</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.1168</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1458</v>
+        <v>0.5487</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1592</v>
+        <v>-0.1411</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0134</v>
+        <v>0.6898</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4477</v>
+        <v>-0.9418</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3299</v>
+        <v>2.7298</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1179</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3945</v>
+        <v>0.9701</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0688</v>
+        <v>2.157</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.6743</v>
+        <v>-1.1869</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7544</v>
+        <v>1.7019</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1565</v>
+        <v>-0.1022</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9109</v>
+        <v>1.804</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9805</v>
+        <v>2.3277</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1864</v>
+        <v>1.0463</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7942</v>
+        <v>1.2813</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2262</v>
+        <v>-0.6258</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3429</v>
+        <v>-1.1485</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1168</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1943</v>
+        <v>0.5518</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.1592</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4473</v>
+        <v>0.3926</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9418</v>
+        <v>-2.4477</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7298</v>
+        <v>-0.3299</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.6716</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3372</v>
+        <v>0.1581</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3036</v>
+        <v>1.8031</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9664</v>
+        <v>-1.6449</v>
       </c>
       <c r="G16" t="n">
         <v>0.4632</v>
@@ -1702,13 +1702,13 @@
         <v>0.3881</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4367</v>
+        <v>0.2577</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0318</v>
+        <v>0.5313</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5951</v>
+        <v>-0.2736</v>
       </c>
       <c r="V16" t="n">
         <v>0.9896</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.195</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4487</v>
+        <v>0.9097</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3627</v>
+        <v>-1.1046</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3137</v>
+        <v>0.545</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3081</v>
+        <v>0.2669</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0056</v>
+        <v>0.2781</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3213</v>
+        <v>1.4696</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3213</v>
+        <v>0.7744</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.6952</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.635</v>
+        <v>-0.9246</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6294</v>
+        <v>-0.5075</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0056</v>
+        <v>-0.4171</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3699</v>
+        <v>0.3182</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4856</v>
+        <v>0.4102</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1157</v>
+        <v>-0.092</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6119</v>
+        <v>-0.2821</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0438</v>
+        <v>-0.2415</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5251</v>
+        <v>0.1484</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5689</v>
+        <v>-0.3899</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0077</v>
+        <v>-0.3137</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2364</v>
+        <v>-0.3081</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2441</v>
+        <v>-0.0056</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7933</v>
+        <v>0.3213</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6715</v>
+        <v>0.3213</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1218</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7856</v>
+        <v>-0.635</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9079</v>
+        <v>-0.6294</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1223</v>
+        <v>-0.0056</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4067</v>
+        <v>0.0423</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4497</v>
+        <v>0.1853</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0431</v>
+        <v>-0.143</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8462</v>
+        <v>0.6119</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0.6119</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4791</v>
+        <v>-0.2624</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4384</v>
+        <v>1.2248</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9593</v>
+        <v>-1.4871</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0587</v>
+        <v>0.0077</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0496</v>
+        <v>-0.2364</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1083</v>
+        <v>0.2441</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1889</v>
+        <v>0.7933</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1483</v>
+        <v>0.6715</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0406</v>
+        <v>0.1218</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1302</v>
+        <v>-0.7856</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1979</v>
+        <v>-0.9079</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0677</v>
+        <v>0.1223</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9085</v>
+        <v>0.1881</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.581</v>
+        <v>0.1494</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4895</v>
+        <v>0.0387</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2821</v>
+        <v>-0.8462</v>
       </c>
       <c r="W19" t="n">
-        <v>0.894</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1761</v>
+        <v>-1.1283</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5253</v>
+        <v>-0.9241</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0098</v>
+        <v>-1.3383</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5351</v>
+        <v>0.4142</v>
       </c>
       <c r="G20" t="n">
-        <v>0.545</v>
+        <v>0.0587</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2669</v>
+        <v>-1.0496</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2781</v>
+        <v>1.1083</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4696</v>
+        <v>0.1889</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7744</v>
+        <v>0.1483</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6952</v>
+        <v>0.0406</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9246</v>
+        <v>-0.1302</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5075</v>
+        <v>-1.1979</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4171</v>
+        <v>1.0677</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7761</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0121</v>
+        <v>0.4635</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5103</v>
+        <v>-0.4809</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5224</v>
+        <v>0.9444</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2821</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6967</v>
+        <v>-1.3809</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2335</v>
+        <v>-0.8331</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4632</v>
+        <v>-0.5478</v>
       </c>
       <c r="G21" t="n">
         <v>2.39</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3405</v>
+        <v>-0.0247</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9444</v>
+        <v>-0.544</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6039</v>
+        <v>0.5193</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.036</v>
+        <v>-2.7846</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7013</v>
+        <v>-1.8014</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3347</v>
+        <v>-0.9832</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4849</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5332</v>
+        <v>-0.2818</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3859</v>
+        <v>-0.486</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1473</v>
+        <v>0.2042</v>
       </c>
       <c r="V22" t="n">
         <v>0.5642</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.435400000000001</v>
+        <v>4.769799999999999</v>
       </c>
       <c r="E23" t="n">
         <v>12.7041</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.268699999999999</v>
+        <v>-7.934</v>
       </c>
       <c r="G23" t="n">
         <v>7.786800000000001</v>
@@ -2218,7 +2218,7 @@
         <v>1.0299</v>
       </c>
       <c r="I23" t="n">
-        <v>6.756800000000001</v>
+        <v>6.7568</v>
       </c>
       <c r="J23" t="n">
         <v>13.8713</v>
@@ -2239,7 +2239,7 @@
         <v>3.2253</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.791099999999999</v>
+        <v>-6.7911</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.5524</v>
@@ -2248,13 +2248,13 @@
         <v>7.7613</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2113</v>
+        <v>2.545799999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1686999999999999</v>
+        <v>-0.1687</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3799</v>
+        <v>2.7145</v>
       </c>
       <c r="V23" t="n">
         <v>1.2284</v>
